--- a/reports/20260727-20260802/城市经理问题闭环填写表_20260727-20260802.xlsx
+++ b/reports/20260727-20260802/城市经理问题闭环填写表_20260727-20260802.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8e0d3742e26940ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R14fa629b651e436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Rf3fdb14cd6134471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R48653376e0464e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R72534dd54d30412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rc3579e8e80d942ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R890733426e3e42f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R96457aff41af420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rd5b7317f32f14b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rb761f8eb60e541ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -507,7 +507,7 @@
         <x:v>新签营收</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>新签营收=总营收-总续卡金额；小程序“新卡金额”只作为卡型原始值留档，不替代新签营收。</x:v>
+        <x:v>一般门店新签营收=总营收-总续卡金额；武汉荟聚按用户2026-08-04确认截图直接使用18,565元。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -531,7 +531,7 @@
         <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数÷新签卡数；正式19店新签卡609张，卡型277/266/66。</x:v>
+        <x:v>一般门店新签小/中/大卡率=对应卡数÷新签卡数；武汉荟聚按用户确认截图直接使用41%/45%/4%。正式19店新签卡609张。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -893,17 +893,17 @@
         <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>完成率上周68.71%→本周68.34%线100% · 继续恶化续卡占比上周11.92%→本周9.65%线15% · 继续恶化</x:v>
+        <x:v>完成率上周68.71%→本周68.34%线100% · 继续恶化续卡占比上周11.92%→本周21.30%线15% · 已过线</x:v>
       </x:c>
       <x:c r="D15" s="18"/>
       <x:c r="E15" s="11" t="str">
-        <x:v>新客数96 → 97↑1.0%老客数88 → 84↓4.5%总营收¥30,206 → ¥30,043.05↓0.5%完成率68.71% → 68.34%↓0.4个百分点 · 线100%新签营收¥26,606 → ¥27,143.05↑2.0%新签办卡率59.38% → 50.52%↓8.9个百分点 · 线40%新签小卡率— → 40.82%— · 线40%新签中卡率— → 46.94%—新签大卡率— → 12.24%—续费率4.55% → 7.14%↑2.6个百分点续卡金额¥3,600 → ¥2,900↓19.4%续卡占比11.92% → 9.65%↓2.3个百分点 · 线15%总引流金额¥19,288 → ¥16,847↓12.7%总引流占比63.85% → 56.08%↓7.8个百分点 · 线25%扫楼金额¥7,715 → ¥7,407↓4.0%扫楼占比25.54% → 24.65%↓0.9个百分点 · 线15%大卡率— → 61.82%— · 线60%</x:v>
+        <x:v>新客数96 → 97↑1.0%老客数88 → 84↓4.5%总营收¥30,206 → ¥30,043.05↓0.5%完成率68.71% → 68.34%↓0.4个百分点 · 线100%新签营收¥26,606 → ¥18,565↓30.2%新签办卡率59.38% → 46.00%↓13.4个百分点 · 线40%新签小卡率— → 41.00%— · 线40%新签中卡率— → 45.00%—新签大卡率— → 4.00%—续费率4.55% → 7.14%↑2.6个百分点续卡金额¥3,600 → ¥6,400↑77.8%续卡占比11.92% → 21.30%↑9.4个百分点 · 线15%总引流金额¥19,288 → ¥16,847↓12.7%总引流占比63.85% → 56.08%↓7.8个百分点 · 线25%扫楼金额¥7,715 → ¥7,407↓4.0%扫楼占比25.54% → 24.65%↓0.9个百分点 · 线15%大卡率— → 61.82%— · 线60%</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>1. 新客96→97增加1人，但总营收反而少¥162.95，新签营收增加¥537.05。请把损失拆到未办卡人数、平均新签客单和卡型降档，不要归因成‘客流不好’。
-2. 新签小/中/大卡为20/23/6张，小卡率40.82%超过40%。请抽查3笔小卡：谁接待、先报哪档、客户在哪句话拒绝升档；下周哪名员工先改？
+        <x:v>1. 新客96→97增加1人，但总营收反而少¥162.95，新签营收少¥8,041。请把损失拆到未办卡人数、平均新签客单和卡型降档，不要归因成‘客流不好’。
+2. 新签小/中/大卡为20/23/6张，小卡率41.00%超过40%。请抽查3笔小卡：谁接待、先报哪档、客户在哪句话拒绝升档；下周哪名员工先改？
 3. 总引流56.08%、扫楼24.65%都已过线，完成率仍只有68.34%。短板不在入口客流：引流客到店后有多少体验、办卡、升中大卡？漏斗断在哪一步？
-4. 上周承诺摘要是“完成率76.89%，距离100%差23.11个百分点。；新客由124人下降至98人，减少26人。；新签营收减少7,525元，下降23.6%。；总引流金额下降11.7%。；2. 新签小/中/大卡为37/14/6张，小卡率64.91%超过40%”。本周续费率7.14%、续卡占比9.65%（线15%）。哪项动作真正执行并产生结果，哪项没有执行？请提供日报、名单或订单证据。</x:v>
+4. 上周承诺摘要是“完成率76.89%，距离100%差23.11个百分点。；新客由124人下降至98人，减少26人。；新签营收减少7,525元，下降23.6%。；总引流金额下降11.7%。；2. 新签小/中/大卡为37/14/6张，小卡率64.91%超过40%”。本周续费率7.14%、续卡占比21.30%（线15%）。哪项动作真正执行并产生结果，哪项没有执行？请提供日报、名单或订单证据。</x:v>
       </x:c>
       <x:c r="G15" s="18"/>
     </x:row>
@@ -1020,7 +1020,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09bbf92b139c448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra343687ae37a4661"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1196,7 +1196,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6068b5df0ed04059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8046b3100c042be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1394,7 +1394,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd101158364764791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15c41e870d0f4f87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1443,17 +1443,17 @@
         <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="C2" s="17" t="str">
-        <x:v>完成率上周68.71%→本周68.34%线100% · 继续恶化续卡占比上周11.92%→本周9.65%线15% · 继续恶化</x:v>
+        <x:v>完成率上周68.71%→本周68.34%线100% · 继续恶化续卡占比上周11.92%→本周21.30%线15% · 已过线</x:v>
       </x:c>
       <x:c r="D2" s="18"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>新客数96 → 97↑1.0%老客数88 → 84↓4.5%总营收¥30,206 → ¥30,043.05↓0.5%完成率68.71% → 68.34%↓0.4个百分点 · 线100%新签营收¥26,606 → ¥27,143.05↑2.0%新签办卡率59.38% → 50.52%↓8.9个百分点 · 线40%新签小卡率— → 40.82%— · 线40%新签中卡率— → 46.94%—新签大卡率— → 12.24%—续费率4.55% → 7.14%↑2.6个百分点续卡金额¥3,600 → ¥2,900↓19.4%续卡占比11.92% → 9.65%↓2.3个百分点 · 线15%总引流金额¥19,288 → ¥16,847↓12.7%总引流占比63.85% → 56.08%↓7.8个百分点 · 线25%扫楼金额¥7,715 → ¥7,407↓4.0%扫楼占比25.54% → 24.65%↓0.9个百分点 · 线15%大卡率— → 61.82%— · 线60%</x:v>
+        <x:v>新客数96 → 97↑1.0%老客数88 → 84↓4.5%总营收¥30,206 → ¥30,043.05↓0.5%完成率68.71% → 68.34%↓0.4个百分点 · 线100%新签营收¥26,606 → ¥18,565↓30.2%新签办卡率59.38% → 46.00%↓13.4个百分点 · 线40%新签小卡率— → 41.00%— · 线40%新签中卡率— → 45.00%—新签大卡率— → 4.00%—续费率4.55% → 7.14%↑2.6个百分点续卡金额¥3,600 → ¥6,400↑77.8%续卡占比11.92% → 21.30%↑9.4个百分点 · 线15%总引流金额¥19,288 → ¥16,847↓12.7%总引流占比63.85% → 56.08%↓7.8个百分点 · 线25%扫楼金额¥7,715 → ¥7,407↓4.0%扫楼占比25.54% → 24.65%↓0.9个百分点 · 线15%大卡率— → 61.82%— · 线60%</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>1. 新客96→97增加1人，但总营收反而少¥162.95，新签营收增加¥537.05。请把损失拆到未办卡人数、平均新签客单和卡型降档，不要归因成‘客流不好’。
-2. 新签小/中/大卡为20/23/6张，小卡率40.82%超过40%。请抽查3笔小卡：谁接待、先报哪档、客户在哪句话拒绝升档；下周哪名员工先改？
+        <x:v>1. 新客96→97增加1人，但总营收反而少¥162.95，新签营收少¥8,041。请把损失拆到未办卡人数、平均新签客单和卡型降档，不要归因成‘客流不好’。
+2. 新签小/中/大卡为20/23/6张，小卡率41.00%超过40%。请抽查3笔小卡：谁接待、先报哪档、客户在哪句话拒绝升档；下周哪名员工先改？
 3. 总引流56.08%、扫楼24.65%都已过线，完成率仍只有68.34%。短板不在入口客流：引流客到店后有多少体验、办卡、升中大卡？漏斗断在哪一步？
-4. 上周承诺摘要是“完成率76.89%，距离100%差23.11个百分点。；新客由124人下降至98人，减少26人。；新签营收减少7,525元，下降23.6%。；总引流金额下降11.7%。；2. 新签小/中/大卡为37/14/6张，小卡率64.91%超过40%”。本周续费率7.14%、续卡占比9.65%（线15%）。哪项动作真正执行并产生结果，哪项没有执行？请提供日报、名单或订单证据。</x:v>
+4. 上周承诺摘要是“完成率76.89%，距离100%差23.11个百分点。；新客由124人下降至98人，减少26人。；新签营收减少7,525元，下降23.6%。；总引流金额下降11.7%。；2. 新签小/中/大卡为37/14/6张，小卡率64.91%超过40%”。本周续费率7.14%、续卡占比21.30%（线15%）。哪项动作真正执行并产生结果，哪项没有执行？请提供日报、名单或订单证据。</x:v>
       </x:c>
       <x:c r="G2" s="18"/>
     </x:row>
@@ -1570,7 +1570,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R273c3f812a094ea4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15e31d6b5bc4f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260727-20260802/城市经理问题闭环填写表_20260727-20260802.xlsx
+++ b/reports/20260727-20260802/城市经理问题闭环填写表_20260727-20260802.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rc3579e8e80d942ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R890733426e3e42f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R96457aff41af420c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rd5b7317f32f14b04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rb761f8eb60e541ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R36e3f071536c4e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R099c78029cf849aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Ra4cc1924548b4452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rfb5857cd50b64727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rfe3187566c334289"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,7 +63,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -100,6 +100,16 @@
         <x:fgColor rgb="FF07835A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7193F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE68600"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -121,7 +131,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -199,6 +209,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -600,7 +616,7 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="118" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
@@ -622,7 +638,7 @@
       <x:c r="G2" s="18"/>
     </x:row>
     <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
@@ -644,7 +660,7 @@
       <x:c r="G3" s="18"/>
     </x:row>
     <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
@@ -666,7 +682,7 @@
       <x:c r="G4" s="18"/>
     </x:row>
     <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
@@ -688,7 +704,7 @@
       <x:c r="G5" s="18"/>
     </x:row>
     <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
@@ -710,7 +726,7 @@
       <x:c r="G6" s="18"/>
     </x:row>
     <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
@@ -732,7 +748,7 @@
       <x:c r="G7" s="18"/>
     </x:row>
     <x:row r="8" ht="118" customHeight="1">
-      <x:c r="A8" s="16" t="str">
+      <x:c r="A8" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
@@ -754,7 +770,7 @@
       <x:c r="G8" s="18"/>
     </x:row>
     <x:row r="9" ht="118" customHeight="1">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
@@ -776,7 +792,7 @@
       <x:c r="G9" s="18"/>
     </x:row>
     <x:row r="10" ht="118" customHeight="1">
-      <x:c r="A10" s="16" t="str">
+      <x:c r="A10" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
@@ -798,7 +814,7 @@
       <x:c r="G10" s="18"/>
     </x:row>
     <x:row r="11" ht="118" customHeight="1">
-      <x:c r="A11" s="16" t="str">
+      <x:c r="A11" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
@@ -820,7 +836,7 @@
       <x:c r="G11" s="18"/>
     </x:row>
     <x:row r="12" ht="118" customHeight="1">
-      <x:c r="A12" s="22" t="str">
+      <x:c r="A12" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
@@ -842,7 +858,7 @@
       <x:c r="G12" s="18"/>
     </x:row>
     <x:row r="13" ht="118" customHeight="1">
-      <x:c r="A13" s="22" t="str">
+      <x:c r="A13" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
@@ -864,7 +880,7 @@
       <x:c r="G13" s="18"/>
     </x:row>
     <x:row r="14" ht="118" customHeight="1">
-      <x:c r="A14" s="26" t="str">
+      <x:c r="A14" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
@@ -886,7 +902,7 @@
       <x:c r="G14" s="18"/>
     </x:row>
     <x:row r="15" ht="118" customHeight="1">
-      <x:c r="A15" s="16" t="str">
+      <x:c r="A15" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
@@ -908,7 +924,7 @@
       <x:c r="G15" s="18"/>
     </x:row>
     <x:row r="16" ht="118" customHeight="1">
-      <x:c r="A16" s="16" t="str">
+      <x:c r="A16" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
@@ -930,7 +946,7 @@
       <x:c r="G16" s="18"/>
     </x:row>
     <x:row r="17" ht="118" customHeight="1">
-      <x:c r="A17" s="16" t="str">
+      <x:c r="A17" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
@@ -952,7 +968,7 @@
       <x:c r="G17" s="18"/>
     </x:row>
     <x:row r="18" ht="118" customHeight="1">
-      <x:c r="A18" s="16" t="str">
+      <x:c r="A18" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
@@ -974,7 +990,7 @@
       <x:c r="G18" s="18"/>
     </x:row>
     <x:row r="19" ht="118" customHeight="1">
-      <x:c r="A19" s="16" t="str">
+      <x:c r="A19" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
@@ -996,7 +1012,7 @@
       <x:c r="G19" s="18"/>
     </x:row>
     <x:row r="20" ht="118" customHeight="1">
-      <x:c r="A20" s="22" t="str">
+      <x:c r="A20" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
@@ -1020,7 +1036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra343687ae37a4661"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd235508913c481a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1062,7 +1078,7 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="118" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
@@ -1084,7 +1100,7 @@
       <x:c r="G2" s="18"/>
     </x:row>
     <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
@@ -1106,7 +1122,7 @@
       <x:c r="G3" s="18"/>
     </x:row>
     <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
@@ -1128,7 +1144,7 @@
       <x:c r="G4" s="18"/>
     </x:row>
     <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
@@ -1150,7 +1166,7 @@
       <x:c r="G5" s="18"/>
     </x:row>
     <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
@@ -1172,7 +1188,7 @@
       <x:c r="G6" s="18"/>
     </x:row>
     <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
@@ -1196,7 +1212,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8046b3100c042be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37c230b81ba74756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1238,7 +1254,7 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="118" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
@@ -1260,7 +1276,7 @@
       <x:c r="G2" s="18"/>
     </x:row>
     <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
@@ -1282,7 +1298,7 @@
       <x:c r="G3" s="18"/>
     </x:row>
     <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
@@ -1304,7 +1320,7 @@
       <x:c r="G4" s="18"/>
     </x:row>
     <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
@@ -1326,7 +1342,7 @@
       <x:c r="G5" s="18"/>
     </x:row>
     <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
@@ -1348,7 +1364,7 @@
       <x:c r="G6" s="18"/>
     </x:row>
     <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
@@ -1370,7 +1386,7 @@
       <x:c r="G7" s="18"/>
     </x:row>
     <x:row r="8" ht="118" customHeight="1">
-      <x:c r="A8" s="26" t="str">
+      <x:c r="A8" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
@@ -1394,7 +1410,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15c41e870d0f4f87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934247b8ff274195"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1436,7 +1452,7 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="118" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
@@ -1458,7 +1474,7 @@
       <x:c r="G2" s="18"/>
     </x:row>
     <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
@@ -1480,7 +1496,7 @@
       <x:c r="G3" s="18"/>
     </x:row>
     <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
@@ -1502,7 +1518,7 @@
       <x:c r="G4" s="18"/>
     </x:row>
     <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="28" t="str">
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
@@ -1524,7 +1540,7 @@
       <x:c r="G5" s="18"/>
     </x:row>
     <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
@@ -1546,7 +1562,7 @@
       <x:c r="G6" s="18"/>
     </x:row>
     <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="29" t="str">
         <x:v>黄灯</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
@@ -1570,7 +1586,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15e31d6b5bc4f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc91bd1ae11094bc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>